--- a/shared_github_workshop.xlsx
+++ b/shared_github_workshop.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRKD\Git testing\Test\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRKD\Git testing\Testing\Repo-for-workshops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0581745-BB31-412B-A0BB-F57FB2E198F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47408BBD-1092-4AB5-9698-FD96E2F3D6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1312,7 +1312,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>18</v>
